--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_model_hyperparameters_configuration.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_model_hyperparameters_configuration.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes (-0.005794 MW)</t>
+          <t>Yes (0.043468 MW)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes (0.002722 MW)</t>
+          <t>Yes (0.008800 MW)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes (0.001869 MW)</t>
+          <t>Yes (0.002246 MW)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yes (-0.013115 MW)</t>
+          <t>Yes (-0.020561 MW)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes (-0.008944 MW)</t>
+          <t>Yes (-0.007211 MW)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yes (0.007462 MW)</t>
+          <t>Yes (0.007701 MW)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
